--- a/01/Documents/TTC 580 Pinout_DEVSAN.xlsx
+++ b/01/Documents/TTC 580 Pinout_DEVSAN.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32BF034-5570-46F2-8F00-07EE3281B143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B29A30-C228-479C-89D1-BAC07AB2831E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="295">
   <si>
     <t>Group</t>
   </si>
@@ -1246,6 +1246,15 @@
   </si>
   <si>
     <t>Ekran</t>
+  </si>
+  <si>
+    <t>Kabin Kapalı Bilgisi</t>
+  </si>
+  <si>
+    <t>Ayak Alıcısı Aktif Bilgisi</t>
+  </si>
+  <si>
+    <t>Çevre Birimi İnput</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1332,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1405,6 +1414,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1539,7 +1554,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1644,14 +1659,27 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1662,19 +1690,33 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1685,6 +1727,9 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1693,54 +1738,37 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2085,21 +2113,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J155"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" customWidth="1"/>
     <col min="4" max="4" width="5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="10" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="10" customWidth="1"/>
-    <col min="8" max="8" width="30.28515625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2118,7 +2146,7 @@
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2132,14 +2160,14 @@
         <v>201</v>
       </c>
       <c r="E2" s="12"/>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="44"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="66"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -2153,14 +2181,14 @@
         <v>202</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="44"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="66"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -2174,14 +2202,14 @@
         <v>203</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="44"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="66"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -2195,14 +2223,14 @@
         <v>204</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="44"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="66"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -2216,14 +2244,14 @@
         <v>205</v>
       </c>
       <c r="E6" s="12"/>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="44"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="66"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -2237,14 +2265,14 @@
         <v>206</v>
       </c>
       <c r="E7" s="12"/>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="44"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="66"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
@@ -2258,14 +2286,14 @@
         <v>246</v>
       </c>
       <c r="E8" s="12"/>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="44"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="66"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
@@ -2279,14 +2307,14 @@
         <v>207</v>
       </c>
       <c r="E9" s="12"/>
-      <c r="F9" s="42" t="s">
+      <c r="F9" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="44"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="66"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -2300,14 +2328,14 @@
         <v>220</v>
       </c>
       <c r="E10" s="12"/>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="38"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="63"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
@@ -2321,14 +2349,14 @@
         <v>118</v>
       </c>
       <c r="E11" s="12"/>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="41"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="46"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
@@ -2342,14 +2370,14 @@
         <v>119</v>
       </c>
       <c r="E12" s="12"/>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="41"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="46"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
@@ -2363,14 +2391,14 @@
         <v>120</v>
       </c>
       <c r="E13" s="12"/>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="41"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="46"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
@@ -2384,14 +2412,14 @@
         <v>121</v>
       </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="41"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="46"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>4</v>
       </c>
@@ -2405,14 +2433,14 @@
         <v>142</v>
       </c>
       <c r="E15" s="12"/>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="41"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
@@ -2426,14 +2454,14 @@
         <v>143</v>
       </c>
       <c r="E16" s="12"/>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="41"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="46"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
@@ -2447,14 +2475,14 @@
         <v>144</v>
       </c>
       <c r="E17" s="12"/>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="41"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="46"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
@@ -2468,14 +2496,14 @@
         <v>145</v>
       </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="41"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="46"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -2489,12 +2517,12 @@
         <v>247</v>
       </c>
       <c r="E19" s="12"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="46"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>15</v>
       </c>
@@ -2508,12 +2536,12 @@
         <v>234</v>
       </c>
       <c r="E20" s="12"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="15"/>
       <c r="I20" s="15"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
@@ -2527,12 +2555,12 @@
         <v>221</v>
       </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -2546,12 +2574,12 @@
         <v>217</v>
       </c>
       <c r="E22" s="15"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
@@ -2565,12 +2593,12 @@
         <v>230</v>
       </c>
       <c r="E23" s="12"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>21</v>
       </c>
@@ -2584,12 +2612,12 @@
         <v>243</v>
       </c>
       <c r="E24" s="12"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>21</v>
       </c>
@@ -2603,12 +2631,12 @@
         <v>244</v>
       </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>21</v>
       </c>
@@ -2622,12 +2650,12 @@
         <v>245</v>
       </c>
       <c r="E26" s="12"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
@@ -2641,12 +2669,12 @@
         <v>256</v>
       </c>
       <c r="E27" s="12"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>21</v>
       </c>
@@ -2660,12 +2688,12 @@
         <v>257</v>
       </c>
       <c r="E28" s="12"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>21</v>
       </c>
@@ -2679,12 +2707,12 @@
         <v>258</v>
       </c>
       <c r="E29" s="12"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>24</v>
       </c>
@@ -2698,10 +2726,10 @@
         <v>103</v>
       </c>
       <c r="E30" s="12"/>
-      <c r="F30" s="57" t="s">
+      <c r="F30" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="G30" s="58" t="s">
+      <c r="G30" s="37" t="s">
         <v>220</v>
       </c>
       <c r="H30" s="15" t="s">
@@ -2709,7 +2737,7 @@
       </c>
       <c r="I30" s="32"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>24</v>
       </c>
@@ -2723,10 +2751,10 @@
         <v>127</v>
       </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="57" t="s">
+      <c r="F31" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="G31" s="58" t="s">
+      <c r="G31" s="37" t="s">
         <v>221</v>
       </c>
       <c r="H31" s="15" t="s">
@@ -2734,7 +2762,7 @@
       </c>
       <c r="I31" s="32"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>24</v>
       </c>
@@ -2750,16 +2778,16 @@
       <c r="E32" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="G32" s="60"/>
+      <c r="G32" s="48"/>
       <c r="H32" s="15" t="s">
         <v>201</v>
       </c>
       <c r="I32" s="32"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>24</v>
       </c>
@@ -2775,10 +2803,10 @@
       <c r="E33" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="G33" s="58" t="s">
+      <c r="G33" s="37" t="s">
         <v>225</v>
       </c>
       <c r="H33" s="15" t="s">
@@ -2786,7 +2814,7 @@
       </c>
       <c r="I33" s="32"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>24</v>
       </c>
@@ -2802,16 +2830,16 @@
       <c r="E34" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="F34" s="59" t="s">
+      <c r="F34" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="G34" s="60"/>
+      <c r="G34" s="48"/>
       <c r="H34" s="15" t="s">
         <v>201</v>
       </c>
       <c r="I34" s="32"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>24</v>
       </c>
@@ -2827,16 +2855,16 @@
       <c r="E35" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="F35" s="59" t="s">
+      <c r="F35" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="G35" s="60"/>
+      <c r="G35" s="48"/>
       <c r="H35" s="15" t="s">
         <v>201</v>
       </c>
       <c r="I35" s="32"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>24</v>
       </c>
@@ -2852,16 +2880,16 @@
       <c r="E36" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="F36" s="59" t="s">
+      <c r="F36" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="G36" s="60"/>
+      <c r="G36" s="48"/>
       <c r="H36" s="15" t="s">
         <v>201</v>
       </c>
       <c r="I36" s="32"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>24</v>
       </c>
@@ -2877,16 +2905,16 @@
       <c r="E37" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="F37" s="59" t="s">
+      <c r="F37" s="47" t="s">
         <v>246</v>
       </c>
-      <c r="G37" s="60"/>
+      <c r="G37" s="48"/>
       <c r="H37" s="15" t="s">
         <v>201</v>
       </c>
       <c r="I37" s="32"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>29</v>
       </c>
@@ -2902,10 +2930,10 @@
       <c r="E38" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="F38" s="61" t="s">
+      <c r="F38" s="38" t="s">
         <v>269</v>
       </c>
-      <c r="G38" s="61" t="s">
+      <c r="G38" s="38" t="s">
         <v>204</v>
       </c>
       <c r="H38" s="15" t="s">
@@ -2915,7 +2943,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>29</v>
       </c>
@@ -2931,10 +2959,10 @@
       <c r="E39" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="F39" s="61" t="s">
+      <c r="F39" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="G39" s="61" t="s">
+      <c r="G39" s="38" t="s">
         <v>203</v>
       </c>
       <c r="H39" s="15" t="s">
@@ -2944,7 +2972,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>29</v>
       </c>
@@ -2960,10 +2988,10 @@
       <c r="E40" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="F40" s="61" t="s">
+      <c r="F40" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="G40" s="61" t="s">
+      <c r="G40" s="38" t="s">
         <v>205</v>
       </c>
       <c r="H40" s="15" t="s">
@@ -2973,7 +3001,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>29</v>
       </c>
@@ -2989,10 +3017,10 @@
       <c r="E41" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="F41" s="61" t="s">
+      <c r="F41" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="G41" s="61" t="s">
+      <c r="G41" s="38" t="s">
         <v>206</v>
       </c>
       <c r="H41" s="15" t="s">
@@ -3002,7 +3030,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>29</v>
       </c>
@@ -3018,10 +3046,10 @@
       <c r="E42" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="F42" s="61" t="s">
+      <c r="F42" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="G42" s="61" t="s">
+      <c r="G42" s="38" t="s">
         <v>203</v>
       </c>
       <c r="H42" s="15" t="s">
@@ -3031,7 +3059,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>29</v>
       </c>
@@ -3047,10 +3075,10 @@
       <c r="E43" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="F43" s="61" t="s">
+      <c r="F43" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="G43" s="61" t="s">
+      <c r="G43" s="38" t="s">
         <v>203</v>
       </c>
       <c r="H43" s="15" t="s">
@@ -3060,7 +3088,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>29</v>
       </c>
@@ -3076,10 +3104,10 @@
       <c r="E44" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="38" t="s">
         <v>206</v>
       </c>
       <c r="H44" s="15" t="s">
@@ -3089,7 +3117,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>29</v>
       </c>
@@ -3105,10 +3133,10 @@
       <c r="E45" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="F45" s="61" t="s">
+      <c r="F45" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="G45" s="61" t="s">
+      <c r="G45" s="38" t="s">
         <v>206</v>
       </c>
       <c r="H45" s="15" t="s">
@@ -3118,7 +3146,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>30</v>
       </c>
@@ -3134,10 +3162,10 @@
       <c r="E46" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="62" t="s">
+      <c r="F46" s="49" t="s">
         <v>275</v>
       </c>
-      <c r="G46" s="63"/>
+      <c r="G46" s="50"/>
       <c r="H46" s="15" t="s">
         <v>267</v>
       </c>
@@ -3145,7 +3173,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>30</v>
       </c>
@@ -3161,10 +3189,10 @@
       <c r="E47" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="F47" s="62" t="s">
+      <c r="F47" s="49" t="s">
         <v>276</v>
       </c>
-      <c r="G47" s="63"/>
+      <c r="G47" s="50"/>
       <c r="H47" s="15" t="s">
         <v>268</v>
       </c>
@@ -3172,7 +3200,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>30</v>
       </c>
@@ -3188,10 +3216,10 @@
       <c r="E48" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="F48" s="59" t="s">
+      <c r="F48" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="G48" s="64"/>
+      <c r="G48" s="51"/>
       <c r="H48" s="16" t="s">
         <v>173</v>
       </c>
@@ -3199,7 +3227,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>30</v>
       </c>
@@ -3215,10 +3243,10 @@
       <c r="E49" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="F49" s="59" t="s">
+      <c r="F49" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="G49" s="64"/>
+      <c r="G49" s="51"/>
       <c r="H49" s="16" t="s">
         <v>174</v>
       </c>
@@ -3226,7 +3254,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>30</v>
       </c>
@@ -3242,10 +3270,10 @@
       <c r="E50" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="F50" s="59" t="s">
+      <c r="F50" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="G50" s="64"/>
+      <c r="G50" s="51"/>
       <c r="H50" s="16" t="s">
         <v>176</v>
       </c>
@@ -3253,7 +3281,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>30</v>
       </c>
@@ -3269,10 +3297,10 @@
       <c r="E51" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F51" s="59" t="s">
+      <c r="F51" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="G51" s="64"/>
+      <c r="G51" s="51"/>
       <c r="H51" s="16" t="s">
         <v>177</v>
       </c>
@@ -3280,7 +3308,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>30</v>
       </c>
@@ -3296,10 +3324,10 @@
       <c r="E52" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="F52" s="59" t="s">
+      <c r="F52" s="47" t="s">
         <v>193</v>
       </c>
-      <c r="G52" s="64"/>
+      <c r="G52" s="51"/>
       <c r="H52" s="16" t="s">
         <v>175</v>
       </c>
@@ -3307,7 +3335,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>30</v>
       </c>
@@ -3323,10 +3351,10 @@
       <c r="E53" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="F53" s="59" t="s">
+      <c r="F53" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="G53" s="60"/>
+      <c r="G53" s="48"/>
       <c r="H53" s="16" t="s">
         <v>178</v>
       </c>
@@ -3334,7 +3362,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>31</v>
       </c>
@@ -3350,16 +3378,16 @@
       <c r="E54" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F54" s="59" t="s">
+      <c r="F54" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="G54" s="60"/>
+      <c r="G54" s="48"/>
       <c r="H54" s="15" t="s">
         <v>201</v>
       </c>
       <c r="I54" s="32"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>31</v>
       </c>
@@ -3375,16 +3403,16 @@
       <c r="E55" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="F55" s="65" t="s">
+      <c r="F55" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="G55" s="66"/>
+      <c r="G55" s="40"/>
       <c r="H55" s="17" t="s">
         <v>201</v>
       </c>
       <c r="I55" s="32"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>31</v>
       </c>
@@ -3400,16 +3428,16 @@
       <c r="E56" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="F56" s="65" t="s">
+      <c r="F56" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="G56" s="66"/>
+      <c r="G56" s="40"/>
       <c r="H56" s="15" t="s">
         <v>201</v>
       </c>
       <c r="I56" s="32"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>31</v>
       </c>
@@ -3423,12 +3451,12 @@
         <v>140</v>
       </c>
       <c r="E57" s="12"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="46"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="43"/>
       <c r="H57" s="15"/>
       <c r="I57" s="32"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>31</v>
       </c>
@@ -3442,12 +3470,11 @@
         <v>117</v>
       </c>
       <c r="E58" s="12"/>
-      <c r="F58" s="13"/>
       <c r="G58" s="14"/>
       <c r="H58" s="15"/>
       <c r="I58" s="32"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>31</v>
       </c>
@@ -3461,12 +3488,14 @@
         <v>141</v>
       </c>
       <c r="E59" s="12"/>
-      <c r="F59" s="13"/>
+      <c r="F59" s="68" t="s">
+        <v>292</v>
+      </c>
       <c r="G59" s="14"/>
       <c r="H59" s="15"/>
       <c r="I59" s="32"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>32</v>
       </c>
@@ -3479,13 +3508,16 @@
       <c r="D60" s="6">
         <v>122</v>
       </c>
-      <c r="E60" s="12"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="32"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E60" s="67"/>
+      <c r="F60" s="68" t="s">
+        <v>293</v>
+      </c>
+      <c r="G60" s="69"/>
+      <c r="H60" s="70"/>
+      <c r="I60" s="70"/>
+      <c r="J60" s="71"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>32</v>
       </c>
@@ -3498,13 +3530,13 @@
       <c r="D61" s="6">
         <v>146</v>
       </c>
-      <c r="E61" s="12"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="32"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E61" s="67"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="70"/>
+      <c r="J61" s="71"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>32</v>
       </c>
@@ -3523,7 +3555,7 @@
       <c r="H62" s="15"/>
       <c r="I62" s="33"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>32</v>
       </c>
@@ -3542,7 +3574,7 @@
       <c r="H63" s="15"/>
       <c r="I63" s="32"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>32</v>
       </c>
@@ -3561,7 +3593,7 @@
       <c r="H64" s="15"/>
       <c r="I64" s="33"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>32</v>
       </c>
@@ -3575,12 +3607,14 @@
         <v>148</v>
       </c>
       <c r="E65" s="18"/>
-      <c r="F65" s="13"/>
+      <c r="F65" s="13" t="s">
+        <v>294</v>
+      </c>
       <c r="G65" s="14"/>
       <c r="H65" s="15"/>
       <c r="I65" s="32"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>33</v>
       </c>
@@ -3596,16 +3630,16 @@
       <c r="E66" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F66" s="59" t="s">
+      <c r="F66" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="G66" s="60"/>
+      <c r="G66" s="48"/>
       <c r="H66" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I66" s="34"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>33</v>
       </c>
@@ -3621,16 +3655,16 @@
       <c r="E67" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F67" s="59" t="s">
+      <c r="F67" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="G67" s="60"/>
+      <c r="G67" s="48"/>
       <c r="H67" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I67" s="34"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>33</v>
       </c>
@@ -3646,16 +3680,16 @@
       <c r="E68" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="F68" s="59" t="s">
+      <c r="F68" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="G68" s="60"/>
+      <c r="G68" s="48"/>
       <c r="H68" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I68" s="34"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>33</v>
       </c>
@@ -3671,16 +3705,16 @@
       <c r="E69" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F69" s="59" t="s">
+      <c r="F69" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="G69" s="60"/>
+      <c r="G69" s="48"/>
       <c r="H69" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I69" s="34"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>33</v>
       </c>
@@ -3696,16 +3730,16 @@
       <c r="E70" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="F70" s="59" t="s">
+      <c r="F70" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="G70" s="60"/>
+      <c r="G70" s="48"/>
       <c r="H70" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I70" s="34"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>33</v>
       </c>
@@ -3721,16 +3755,16 @@
       <c r="E71" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="59" t="s">
+      <c r="F71" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="G71" s="60"/>
+      <c r="G71" s="48"/>
       <c r="H71" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I71" s="34"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>33</v>
       </c>
@@ -3746,16 +3780,16 @@
       <c r="E72" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="F72" s="59" t="s">
+      <c r="F72" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="G72" s="60"/>
+      <c r="G72" s="48"/>
       <c r="H72" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I72" s="34"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>33</v>
       </c>
@@ -3771,16 +3805,16 @@
       <c r="E73" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="F73" s="59" t="s">
+      <c r="F73" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="G73" s="60"/>
+      <c r="G73" s="48"/>
       <c r="H73" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I73" s="34"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>33</v>
       </c>
@@ -3796,16 +3830,16 @@
       <c r="E74" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="F74" s="59" t="s">
+      <c r="F74" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="G74" s="60"/>
+      <c r="G74" s="48"/>
       <c r="H74" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I74" s="34"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>33</v>
       </c>
@@ -3821,16 +3855,16 @@
       <c r="E75" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="F75" s="59" t="s">
+      <c r="F75" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="G75" s="60"/>
+      <c r="G75" s="48"/>
       <c r="H75" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I75" s="34"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>33</v>
       </c>
@@ -3846,16 +3880,16 @@
       <c r="E76" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F76" s="59" t="s">
+      <c r="F76" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="G76" s="60"/>
+      <c r="G76" s="48"/>
       <c r="H76" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I76" s="34"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>33</v>
       </c>
@@ -3871,16 +3905,16 @@
       <c r="E77" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="F77" s="59" t="s">
+      <c r="F77" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="G77" s="60"/>
+      <c r="G77" s="48"/>
       <c r="H77" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I77" s="34"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>33</v>
       </c>
@@ -3896,16 +3930,16 @@
       <c r="E78" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="F78" s="59" t="s">
+      <c r="F78" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="G78" s="60"/>
+      <c r="G78" s="48"/>
       <c r="H78" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I78" s="34"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>33</v>
       </c>
@@ -3921,16 +3955,16 @@
       <c r="E79" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="F79" s="59" t="s">
+      <c r="F79" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="G79" s="60"/>
+      <c r="G79" s="48"/>
       <c r="H79" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I79" s="34"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>33</v>
       </c>
@@ -3946,16 +3980,16 @@
       <c r="E80" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="F80" s="59" t="s">
+      <c r="F80" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="G80" s="60"/>
+      <c r="G80" s="48"/>
       <c r="H80" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I80" s="34"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>33</v>
       </c>
@@ -3971,16 +4005,16 @@
       <c r="E81" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="F81" s="59" t="s">
+      <c r="F81" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="G81" s="60"/>
+      <c r="G81" s="48"/>
       <c r="H81" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I81" s="34"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>33</v>
       </c>
@@ -3996,16 +4030,16 @@
       <c r="E82" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="F82" s="59" t="s">
+      <c r="F82" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="G82" s="64"/>
+      <c r="G82" s="51"/>
       <c r="H82" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I82" s="35"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>33</v>
       </c>
@@ -4021,16 +4055,16 @@
       <c r="E83" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="F83" s="59" t="s">
+      <c r="F83" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="G83" s="64"/>
+      <c r="G83" s="51"/>
       <c r="H83" s="15" t="s">
         <v>284</v>
       </c>
       <c r="I83" s="35"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>33</v>
       </c>
@@ -4044,12 +4078,12 @@
         <v>160</v>
       </c>
       <c r="E84" s="12"/>
-      <c r="F84" s="45"/>
-      <c r="G84" s="51"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="58"/>
       <c r="H84" s="19"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>33</v>
       </c>
@@ -4065,17 +4099,17 @@
       <c r="E85" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F85" s="45" t="s">
+      <c r="F85" s="42" t="s">
         <v>232</v>
       </c>
-      <c r="G85" s="46"/>
+      <c r="G85" s="43"/>
       <c r="H85" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I85" s="27"/>
       <c r="J85" s="4"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>33</v>
       </c>
@@ -4091,17 +4125,17 @@
       <c r="E86" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F86" s="45" t="s">
+      <c r="F86" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="G86" s="46"/>
+      <c r="G86" s="43"/>
       <c r="H86" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I86" s="28"/>
       <c r="J86" s="4"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>33</v>
       </c>
@@ -4117,16 +4151,16 @@
       <c r="E87" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F87" s="45" t="s">
+      <c r="F87" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="G87" s="46"/>
+      <c r="G87" s="43"/>
       <c r="H87" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I87" s="26"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>33</v>
       </c>
@@ -4142,17 +4176,17 @@
       <c r="E88" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F88" s="45" t="s">
+      <c r="F88" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="G88" s="46"/>
+      <c r="G88" s="43"/>
       <c r="H88" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I88" s="28"/>
       <c r="J88" s="4"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>33</v>
       </c>
@@ -4168,17 +4202,17 @@
       <c r="E89" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F89" s="45" t="s">
+      <c r="F89" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="G89" s="46"/>
+      <c r="G89" s="43"/>
       <c r="H89" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I89" s="28"/>
       <c r="J89" s="4"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>33</v>
       </c>
@@ -4194,16 +4228,16 @@
       <c r="E90" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F90" s="45" t="s">
+      <c r="F90" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="G90" s="46"/>
+      <c r="G90" s="43"/>
       <c r="H90" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I90" s="25"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>33</v>
       </c>
@@ -4219,16 +4253,16 @@
       <c r="E91" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F91" s="45" t="s">
+      <c r="F91" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="G91" s="46"/>
+      <c r="G91" s="43"/>
       <c r="H91" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I91" s="25"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>33</v>
       </c>
@@ -4244,16 +4278,16 @@
       <c r="E92" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F92" s="45" t="s">
+      <c r="F92" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="G92" s="46"/>
+      <c r="G92" s="43"/>
       <c r="H92" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I92" s="25"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>33</v>
       </c>
@@ -4267,12 +4301,12 @@
         <v>172</v>
       </c>
       <c r="E93" s="12"/>
-      <c r="F93" s="47"/>
-      <c r="G93" s="48"/>
+      <c r="F93" s="56"/>
+      <c r="G93" s="57"/>
       <c r="H93" s="15"/>
       <c r="I93" s="15"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>36</v>
       </c>
@@ -4286,12 +4320,12 @@
         <v>101</v>
       </c>
       <c r="E94" s="12"/>
-      <c r="F94" s="45"/>
-      <c r="G94" s="46"/>
+      <c r="F94" s="42"/>
+      <c r="G94" s="43"/>
       <c r="H94" s="15"/>
       <c r="I94" s="15"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>36</v>
       </c>
@@ -4305,12 +4339,12 @@
         <v>125</v>
       </c>
       <c r="E95" s="12"/>
-      <c r="F95" s="45"/>
-      <c r="G95" s="46"/>
+      <c r="F95" s="42"/>
+      <c r="G95" s="43"/>
       <c r="H95" s="15"/>
       <c r="I95" s="15"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>36</v>
       </c>
@@ -4324,12 +4358,12 @@
         <v>150</v>
       </c>
       <c r="E96" s="12"/>
-      <c r="F96" s="47"/>
-      <c r="G96" s="48"/>
+      <c r="F96" s="56"/>
+      <c r="G96" s="57"/>
       <c r="H96" s="15"/>
       <c r="I96" s="15"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>36</v>
       </c>
@@ -4343,12 +4377,12 @@
         <v>174</v>
       </c>
       <c r="E97" s="12"/>
-      <c r="F97" s="45"/>
-      <c r="G97" s="46"/>
+      <c r="F97" s="42"/>
+      <c r="G97" s="43"/>
       <c r="H97" s="15"/>
       <c r="I97" s="15"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>36</v>
       </c>
@@ -4364,16 +4398,16 @@
       <c r="E98" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F98" s="47" t="s">
+      <c r="F98" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="G98" s="48"/>
+      <c r="G98" s="57"/>
       <c r="H98" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I98" s="25"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>36</v>
       </c>
@@ -4389,16 +4423,16 @@
       <c r="E99" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F99" s="45" t="s">
+      <c r="F99" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="G99" s="46"/>
+      <c r="G99" s="43"/>
       <c r="H99" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I99" s="25"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>36</v>
       </c>
@@ -4414,16 +4448,16 @@
       <c r="E100" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F100" s="45" t="s">
+      <c r="F100" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="G100" s="46"/>
+      <c r="G100" s="43"/>
       <c r="H100" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I100" s="25"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>36</v>
       </c>
@@ -4439,16 +4473,16 @@
       <c r="E101" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F101" s="47" t="s">
+      <c r="F101" s="56" t="s">
         <v>195</v>
       </c>
-      <c r="G101" s="48"/>
+      <c r="G101" s="57"/>
       <c r="H101" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I101" s="25"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>37</v>
       </c>
@@ -4473,7 +4507,7 @@
       </c>
       <c r="I102" s="25"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>37</v>
       </c>
@@ -4498,7 +4532,7 @@
       </c>
       <c r="I103" s="25"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>37</v>
       </c>
@@ -4523,7 +4557,7 @@
       </c>
       <c r="I104" s="25"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>37</v>
       </c>
@@ -4548,7 +4582,7 @@
       </c>
       <c r="I105" s="25"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>37</v>
       </c>
@@ -4573,7 +4607,7 @@
       </c>
       <c r="I106" s="25"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>37</v>
       </c>
@@ -4589,17 +4623,17 @@
       <c r="E107" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="F107" s="45" t="s">
+      <c r="F107" s="42" t="s">
         <v>194</v>
       </c>
-      <c r="G107" s="46"/>
+      <c r="G107" s="43"/>
       <c r="H107" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I107" s="29"/>
       <c r="J107" s="4"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>37</v>
       </c>
@@ -4615,16 +4649,16 @@
       <c r="E108" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="F108" s="45" t="s">
+      <c r="F108" s="42" t="s">
         <v>279</v>
       </c>
-      <c r="G108" s="46"/>
+      <c r="G108" s="43"/>
       <c r="H108" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I108" s="25"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>37</v>
       </c>
@@ -4640,16 +4674,16 @@
       <c r="E109" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="F109" s="45" t="s">
+      <c r="F109" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="G109" s="46"/>
+      <c r="G109" s="43"/>
       <c r="H109" s="15" t="s">
         <v>235</v>
       </c>
       <c r="I109" s="25"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>40</v>
       </c>
@@ -4663,12 +4697,12 @@
         <v>251</v>
       </c>
       <c r="E110" s="12"/>
-      <c r="F110" s="45"/>
-      <c r="G110" s="46"/>
+      <c r="F110" s="42"/>
+      <c r="G110" s="43"/>
       <c r="H110" s="15"/>
       <c r="I110" s="15"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>40</v>
       </c>
@@ -4682,12 +4716,12 @@
         <v>238</v>
       </c>
       <c r="E111" s="12"/>
-      <c r="F111" s="45"/>
-      <c r="G111" s="46"/>
+      <c r="F111" s="42"/>
+      <c r="G111" s="43"/>
       <c r="H111" s="15"/>
       <c r="I111" s="15"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>40</v>
       </c>
@@ -4701,12 +4735,12 @@
         <v>252</v>
       </c>
       <c r="E112" s="12"/>
-      <c r="F112" s="45"/>
-      <c r="G112" s="46"/>
+      <c r="F112" s="42"/>
+      <c r="G112" s="43"/>
       <c r="H112" s="15"/>
       <c r="I112" s="15"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>40</v>
       </c>
@@ -4720,12 +4754,12 @@
         <v>239</v>
       </c>
       <c r="E113" s="12"/>
-      <c r="F113" s="45"/>
-      <c r="G113" s="46"/>
+      <c r="F113" s="42"/>
+      <c r="G113" s="43"/>
       <c r="H113" s="15"/>
       <c r="I113" s="15"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>40</v>
       </c>
@@ -4739,12 +4773,12 @@
         <v>253</v>
       </c>
       <c r="E114" s="12"/>
-      <c r="F114" s="45"/>
-      <c r="G114" s="46"/>
+      <c r="F114" s="42"/>
+      <c r="G114" s="43"/>
       <c r="H114" s="15"/>
       <c r="I114" s="15"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>40</v>
       </c>
@@ -4758,12 +4792,12 @@
         <v>240</v>
       </c>
       <c r="E115" s="12"/>
-      <c r="F115" s="45"/>
-      <c r="G115" s="46"/>
+      <c r="F115" s="42"/>
+      <c r="G115" s="43"/>
       <c r="H115" s="17"/>
       <c r="I115" s="15"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>40</v>
       </c>
@@ -4777,12 +4811,12 @@
         <v>254</v>
       </c>
       <c r="E116" s="12"/>
-      <c r="F116" s="45"/>
-      <c r="G116" s="51"/>
+      <c r="F116" s="42"/>
+      <c r="G116" s="58"/>
       <c r="H116" s="23"/>
       <c r="I116" s="16"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>40</v>
       </c>
@@ -4796,12 +4830,12 @@
         <v>241</v>
       </c>
       <c r="E117" s="12"/>
-      <c r="F117" s="45"/>
-      <c r="G117" s="46"/>
+      <c r="F117" s="42"/>
+      <c r="G117" s="43"/>
       <c r="H117" s="16"/>
       <c r="I117" s="16"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>41</v>
       </c>
@@ -4815,12 +4849,12 @@
         <v>161</v>
       </c>
       <c r="E118" s="12"/>
-      <c r="F118" s="45"/>
-      <c r="G118" s="46"/>
+      <c r="F118" s="42"/>
+      <c r="G118" s="43"/>
       <c r="H118" s="15"/>
       <c r="I118" s="15"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>41</v>
       </c>
@@ -4834,12 +4868,12 @@
         <v>185</v>
       </c>
       <c r="E119" s="12"/>
-      <c r="F119" s="45"/>
-      <c r="G119" s="51"/>
+      <c r="F119" s="42"/>
+      <c r="G119" s="58"/>
       <c r="H119" s="23"/>
       <c r="I119" s="16"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>41</v>
       </c>
@@ -4853,12 +4887,12 @@
         <v>188</v>
       </c>
       <c r="E120" s="12"/>
-      <c r="F120" s="45"/>
-      <c r="G120" s="51"/>
+      <c r="F120" s="42"/>
+      <c r="G120" s="58"/>
       <c r="H120" s="23"/>
       <c r="I120" s="16"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>41</v>
       </c>
@@ -4872,13 +4906,13 @@
         <v>164</v>
       </c>
       <c r="E121" s="12"/>
-      <c r="F121" s="45"/>
-      <c r="G121" s="51"/>
+      <c r="F121" s="42"/>
+      <c r="G121" s="58"/>
       <c r="H121" s="16"/>
       <c r="I121" s="24"/>
       <c r="J121" s="4"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>41</v>
       </c>
@@ -4892,12 +4926,12 @@
         <v>191</v>
       </c>
       <c r="E122" s="12"/>
-      <c r="F122" s="45"/>
-      <c r="G122" s="51"/>
+      <c r="F122" s="42"/>
+      <c r="G122" s="58"/>
       <c r="H122" s="23"/>
       <c r="I122" s="16"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>41</v>
       </c>
@@ -4911,12 +4945,12 @@
         <v>167</v>
       </c>
       <c r="E123" s="12"/>
-      <c r="F123" s="45"/>
-      <c r="G123" s="51"/>
+      <c r="F123" s="42"/>
+      <c r="G123" s="58"/>
       <c r="H123" s="23"/>
       <c r="I123" s="16"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>41</v>
       </c>
@@ -4930,12 +4964,12 @@
         <v>194</v>
       </c>
       <c r="E124" s="12"/>
-      <c r="F124" s="45"/>
-      <c r="G124" s="51"/>
+      <c r="F124" s="42"/>
+      <c r="G124" s="58"/>
       <c r="H124" s="23"/>
       <c r="I124" s="16"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>41</v>
       </c>
@@ -4949,12 +4983,12 @@
         <v>170</v>
       </c>
       <c r="E125" s="12"/>
-      <c r="F125" s="45"/>
-      <c r="G125" s="46"/>
+      <c r="F125" s="42"/>
+      <c r="G125" s="43"/>
       <c r="H125" s="15"/>
       <c r="I125" s="15"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>42</v>
       </c>
@@ -4968,14 +5002,14 @@
         <v>235</v>
       </c>
       <c r="E126" s="12"/>
-      <c r="F126" s="49" t="s">
+      <c r="F126" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="G126" s="50"/>
+      <c r="G126" s="60"/>
       <c r="H126" s="15"/>
       <c r="I126" s="31"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>42</v>
       </c>
@@ -4989,14 +5023,14 @@
         <v>248</v>
       </c>
       <c r="E127" s="12"/>
-      <c r="F127" s="49" t="s">
+      <c r="F127" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="G127" s="50"/>
+      <c r="G127" s="60"/>
       <c r="H127" s="15"/>
       <c r="I127" s="31"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>47</v>
       </c>
@@ -5010,14 +5044,14 @@
         <v>236</v>
       </c>
       <c r="E128" s="12"/>
-      <c r="F128" s="49" t="s">
+      <c r="F128" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="G128" s="50"/>
+      <c r="G128" s="60"/>
       <c r="H128" s="15"/>
       <c r="I128" s="31"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>47</v>
       </c>
@@ -5031,14 +5065,14 @@
         <v>249</v>
       </c>
       <c r="E129" s="12"/>
-      <c r="F129" s="49" t="s">
+      <c r="F129" s="59" t="s">
         <v>120</v>
       </c>
-      <c r="G129" s="50"/>
+      <c r="G129" s="60"/>
       <c r="H129" s="15"/>
       <c r="I129" s="31"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>52</v>
       </c>
@@ -5052,14 +5086,14 @@
         <v>237</v>
       </c>
       <c r="E130" s="12"/>
-      <c r="F130" s="49" t="s">
+      <c r="F130" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="G130" s="50"/>
+      <c r="G130" s="60"/>
       <c r="H130" s="15"/>
       <c r="I130" s="31"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>52</v>
       </c>
@@ -5073,14 +5107,14 @@
         <v>250</v>
       </c>
       <c r="E131" s="12"/>
-      <c r="F131" s="49" t="s">
+      <c r="F131" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="G131" s="50"/>
+      <c r="G131" s="60"/>
       <c r="H131" s="15"/>
       <c r="I131" s="31"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>57</v>
       </c>
@@ -5094,14 +5128,14 @@
         <v>216</v>
       </c>
       <c r="E132" s="12"/>
-      <c r="F132" s="49" t="s">
+      <c r="F132" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="G132" s="50"/>
+      <c r="G132" s="60"/>
       <c r="H132" s="15"/>
       <c r="I132" s="31"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>57</v>
       </c>
@@ -5115,14 +5149,14 @@
         <v>229</v>
       </c>
       <c r="E133" s="12"/>
-      <c r="F133" s="49" t="s">
+      <c r="F133" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="G133" s="50"/>
+      <c r="G133" s="60"/>
       <c r="H133" s="15"/>
       <c r="I133" s="31"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>62</v>
       </c>
@@ -5136,14 +5170,14 @@
         <v>209</v>
       </c>
       <c r="E134" s="12"/>
-      <c r="F134" s="45" t="s">
+      <c r="F134" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="G134" s="46"/>
+      <c r="G134" s="43"/>
       <c r="H134" s="15"/>
       <c r="I134" s="31"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>62</v>
       </c>
@@ -5157,14 +5191,14 @@
         <v>222</v>
       </c>
       <c r="E135" s="12"/>
-      <c r="F135" s="45" t="s">
+      <c r="F135" s="42" t="s">
         <v>219</v>
       </c>
-      <c r="G135" s="46"/>
+      <c r="G135" s="43"/>
       <c r="H135" s="15"/>
       <c r="I135" s="31"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>67</v>
       </c>
@@ -5180,16 +5214,16 @@
       <c r="E136" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="F136" s="45" t="s">
+      <c r="F136" s="42" t="s">
         <v>257</v>
       </c>
-      <c r="G136" s="46"/>
+      <c r="G136" s="43"/>
       <c r="H136" s="15" t="s">
         <v>288</v>
       </c>
       <c r="I136" s="31"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>67</v>
       </c>
@@ -5205,16 +5239,16 @@
       <c r="E137" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="F137" s="45" t="s">
+      <c r="F137" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="G137" s="46"/>
+      <c r="G137" s="43"/>
       <c r="H137" s="15" t="s">
         <v>288</v>
       </c>
       <c r="I137" s="31"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>72</v>
       </c>
@@ -5228,12 +5262,12 @@
         <v>211</v>
       </c>
       <c r="E138" s="12"/>
-      <c r="F138" s="45"/>
-      <c r="G138" s="46"/>
+      <c r="F138" s="42"/>
+      <c r="G138" s="43"/>
       <c r="H138" s="15"/>
       <c r="I138" s="15"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>72</v>
       </c>
@@ -5247,12 +5281,12 @@
         <v>224</v>
       </c>
       <c r="E139" s="12"/>
-      <c r="F139" s="45"/>
-      <c r="G139" s="46"/>
+      <c r="F139" s="42"/>
+      <c r="G139" s="43"/>
       <c r="H139" s="15"/>
       <c r="I139" s="15"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>77</v>
       </c>
@@ -5266,12 +5300,12 @@
         <v>212</v>
       </c>
       <c r="E140" s="12"/>
-      <c r="F140" s="45"/>
-      <c r="G140" s="46"/>
+      <c r="F140" s="42"/>
+      <c r="G140" s="43"/>
       <c r="H140" s="15"/>
       <c r="I140" s="15"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>77</v>
       </c>
@@ -5285,12 +5319,12 @@
         <v>225</v>
       </c>
       <c r="E141" s="12"/>
-      <c r="F141" s="45"/>
-      <c r="G141" s="46"/>
+      <c r="F141" s="42"/>
+      <c r="G141" s="43"/>
       <c r="H141" s="15"/>
       <c r="I141" s="15"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>82</v>
       </c>
@@ -5304,17 +5338,17 @@
         <v>213</v>
       </c>
       <c r="E142" s="12"/>
-      <c r="F142" s="45" t="s">
+      <c r="F142" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="G142" s="46"/>
+      <c r="G142" s="43"/>
       <c r="H142" s="15" t="s">
         <v>290</v>
       </c>
       <c r="I142" s="31"/>
-      <c r="J142" s="56"/>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J142" s="41"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>82</v>
       </c>
@@ -5328,17 +5362,17 @@
         <v>226</v>
       </c>
       <c r="E143" s="12"/>
-      <c r="F143" s="45" t="s">
+      <c r="F143" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="G143" s="46"/>
+      <c r="G143" s="43"/>
       <c r="H143" s="15" t="s">
         <v>290</v>
       </c>
       <c r="I143" s="31"/>
-      <c r="J143" s="56"/>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J143" s="41"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>87</v>
       </c>
@@ -5354,17 +5388,17 @@
       <c r="E144" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="F144" s="45" t="s">
+      <c r="F144" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="G144" s="46"/>
+      <c r="G144" s="43"/>
       <c r="H144" s="15" t="s">
         <v>291</v>
       </c>
       <c r="I144" s="31"/>
-      <c r="J144" s="56"/>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J144" s="41"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>87</v>
       </c>
@@ -5380,17 +5414,17 @@
       <c r="E145" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="F145" s="45" t="s">
+      <c r="F145" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="G145" s="46"/>
+      <c r="G145" s="43"/>
       <c r="H145" s="15" t="s">
         <v>291</v>
       </c>
       <c r="I145" s="31"/>
-      <c r="J145" s="56"/>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J145" s="41"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>92</v>
       </c>
@@ -5404,17 +5438,17 @@
         <v>215</v>
       </c>
       <c r="E146" s="12"/>
-      <c r="F146" s="45" t="s">
+      <c r="F146" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="G146" s="46"/>
+      <c r="G146" s="43"/>
       <c r="H146" s="15" t="s">
         <v>289</v>
       </c>
       <c r="I146" s="31"/>
-      <c r="J146" s="56"/>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J146" s="41"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>92</v>
       </c>
@@ -5428,17 +5462,17 @@
         <v>228</v>
       </c>
       <c r="E147" s="12"/>
-      <c r="F147" s="45" t="s">
+      <c r="F147" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="G147" s="46"/>
+      <c r="G147" s="43"/>
       <c r="H147" s="15" t="s">
         <v>289</v>
       </c>
       <c r="I147" s="31"/>
-      <c r="J147" s="56"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J147" s="41"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>97</v>
       </c>
@@ -5452,12 +5486,12 @@
         <v>218</v>
       </c>
       <c r="E148" s="12"/>
-      <c r="F148" s="45"/>
-      <c r="G148" s="46"/>
+      <c r="F148" s="42"/>
+      <c r="G148" s="43"/>
       <c r="H148" s="15"/>
       <c r="I148" s="15"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>97</v>
       </c>
@@ -5471,12 +5505,12 @@
         <v>219</v>
       </c>
       <c r="E149" s="12"/>
-      <c r="F149" s="45"/>
-      <c r="G149" s="46"/>
+      <c r="F149" s="42"/>
+      <c r="G149" s="43"/>
       <c r="H149" s="15"/>
       <c r="I149" s="15"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>97</v>
       </c>
@@ -5490,12 +5524,12 @@
         <v>231</v>
       </c>
       <c r="E150" s="12"/>
-      <c r="F150" s="45"/>
-      <c r="G150" s="46"/>
+      <c r="F150" s="42"/>
+      <c r="G150" s="43"/>
       <c r="H150" s="15"/>
       <c r="I150" s="15"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>97</v>
       </c>
@@ -5509,12 +5543,12 @@
         <v>232</v>
       </c>
       <c r="E151" s="12"/>
-      <c r="F151" s="45"/>
-      <c r="G151" s="46"/>
+      <c r="F151" s="42"/>
+      <c r="G151" s="43"/>
       <c r="H151" s="15"/>
       <c r="I151" s="15"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>105</v>
       </c>
@@ -5528,12 +5562,12 @@
         <v>242</v>
       </c>
       <c r="E152" s="12"/>
-      <c r="F152" s="45"/>
-      <c r="G152" s="46"/>
+      <c r="F152" s="42"/>
+      <c r="G152" s="43"/>
       <c r="H152" s="15"/>
       <c r="I152" s="15"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>105</v>
       </c>
@@ -5547,12 +5581,12 @@
         <v>255</v>
       </c>
       <c r="E153" s="12"/>
-      <c r="F153" s="45"/>
-      <c r="G153" s="46"/>
+      <c r="F153" s="42"/>
+      <c r="G153" s="43"/>
       <c r="H153" s="15"/>
       <c r="I153" s="15"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>110</v>
       </c>
@@ -5566,12 +5600,12 @@
         <v>208</v>
       </c>
       <c r="E154" s="12"/>
-      <c r="F154" s="45"/>
-      <c r="G154" s="46"/>
+      <c r="F154" s="42"/>
+      <c r="G154" s="43"/>
       <c r="H154" s="15"/>
       <c r="I154" s="15"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>112</v>
       </c>
@@ -5585,10 +5619,10 @@
         <v>233</v>
       </c>
       <c r="E155" s="12"/>
-      <c r="F155" s="45" t="s">
+      <c r="F155" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="G155" s="46"/>
+      <c r="G155" s="43"/>
       <c r="H155" s="15"/>
       <c r="I155" s="15"/>
     </row>
@@ -5600,6 +5634,118 @@
     <protectedRange sqref="I86:I89" name="Function_Descriptions_Search_13_1_1"/>
   </protectedRanges>
   <mergeCells count="136">
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="F155:G155"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="F152:G152"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="F150:G150"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="F148:G148"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F139:G139"/>
+    <mergeCell ref="F138:G138"/>
+    <mergeCell ref="F147:G147"/>
+    <mergeCell ref="F146:G146"/>
+    <mergeCell ref="F145:G145"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F143:G143"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="F135:G135"/>
+    <mergeCell ref="F134:G134"/>
+    <mergeCell ref="F133:G133"/>
+    <mergeCell ref="F132:G132"/>
+    <mergeCell ref="F131:G131"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="F128:G128"/>
+    <mergeCell ref="F127:G127"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F69:G69"/>
     <mergeCell ref="J144:J145"/>
     <mergeCell ref="J146:J147"/>
     <mergeCell ref="F20:G20"/>
@@ -5624,118 +5770,6 @@
     <mergeCell ref="F46:G46"/>
     <mergeCell ref="F47:G47"/>
     <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F125:G125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="F121:G121"/>
-    <mergeCell ref="F120:G120"/>
-    <mergeCell ref="F119:G119"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="F115:G115"/>
-    <mergeCell ref="F114:G114"/>
-    <mergeCell ref="F113:G113"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="F110:G110"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="F135:G135"/>
-    <mergeCell ref="F134:G134"/>
-    <mergeCell ref="F133:G133"/>
-    <mergeCell ref="F132:G132"/>
-    <mergeCell ref="F131:G131"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="F128:G128"/>
-    <mergeCell ref="F127:G127"/>
-    <mergeCell ref="F126:G126"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="F155:G155"/>
-    <mergeCell ref="F154:G154"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="F152:G152"/>
-    <mergeCell ref="F151:G151"/>
-    <mergeCell ref="F150:G150"/>
-    <mergeCell ref="F149:G149"/>
-    <mergeCell ref="F148:G148"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F139:G139"/>
-    <mergeCell ref="F138:G138"/>
-    <mergeCell ref="F147:G147"/>
-    <mergeCell ref="F146:G146"/>
-    <mergeCell ref="F145:G145"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="F143:G143"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="F4:I4"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
